--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22733,7 +22733,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22746,12 +22746,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -22781,7 +22781,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25949,7 +25949,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -25997,7 +25997,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26010,12 +26010,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27293,7 +27293,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27306,12 +27306,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28218,12 +28218,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28301,7 +28301,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28314,12 +28314,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28781,7 +28781,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -28794,12 +28794,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29453,7 +29453,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29501,7 +29501,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30845,7 +30845,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -30858,12 +30858,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -30906,12 +30906,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31277,7 +31277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31290,12 +31290,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31386,12 +31386,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31578,12 +31578,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -32778,12 +32778,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33917,7 +33917,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -33930,12 +33930,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -33978,12 +33978,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34157,7 +34157,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34170,12 +34170,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34829,7 +34829,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -34842,12 +34842,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35309,7 +35309,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35405,7 +35405,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35418,12 +35418,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35549,7 +35549,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35562,12 +35562,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35741,7 +35741,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -35754,12 +35754,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -35789,7 +35789,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -35802,12 +35802,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -35837,7 +35837,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -35850,12 +35850,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -35981,7 +35981,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -35994,12 +35994,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36077,7 +36077,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36269,7 +36269,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36282,12 +36282,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36557,7 +36557,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36570,12 +36570,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36749,7 +36749,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -36762,12 +36762,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36941,7 +36941,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37085,7 +37085,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37098,12 +37098,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37181,7 +37181,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37194,12 +37194,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37325,7 +37325,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37338,12 +37338,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38141,7 +38141,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38154,12 +38154,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38189,7 +38189,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38202,12 +38202,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38237,7 +38237,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38250,12 +38250,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38298,12 +38298,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38333,7 +38333,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38346,12 +38346,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38381,7 +38381,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38394,12 +38394,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38429,7 +38429,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38442,12 +38442,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39197,7 +39197,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39210,12 +39210,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39389,7 +39389,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39402,12 +39402,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22733,7 +22733,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22746,12 +22746,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -22781,7 +22781,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25949,7 +25949,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -25997,7 +25997,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26010,12 +26010,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29453,7 +29453,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29501,7 +29501,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30845,7 +30845,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -30858,12 +30858,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -30906,12 +30906,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -32778,12 +32778,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -32826,12 +32826,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33293,7 +33293,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33306,12 +33306,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33437,7 +33437,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33450,12 +33450,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33917,7 +33917,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -33930,12 +33930,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34157,7 +34157,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34170,12 +34170,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35309,7 +35309,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35405,7 +35405,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35418,12 +35418,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35549,7 +35549,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35562,12 +35562,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35741,7 +35741,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -35754,12 +35754,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -35789,7 +35789,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -35802,12 +35802,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -35837,7 +35837,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -35850,12 +35850,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -35981,7 +35981,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -35994,12 +35994,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36077,7 +36077,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36269,7 +36269,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36282,12 +36282,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36557,7 +36557,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36570,12 +36570,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36701,7 +36701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -36714,12 +36714,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37085,7 +37085,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37098,12 +37098,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37181,7 +37181,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37194,12 +37194,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37325,7 +37325,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37338,12 +37338,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38093,7 +38093,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38106,12 +38106,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38237,7 +38237,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38250,12 +38250,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38298,12 +38298,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38333,7 +38333,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38346,12 +38346,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38381,7 +38381,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38394,12 +38394,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39149,7 +39149,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39162,12 +39162,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39197,7 +39197,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39210,12 +39210,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39245,7 +39245,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39258,12 +39258,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39293,7 +39293,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39306,12 +39306,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39389,7 +39389,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39402,12 +39402,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21813,7 +21813,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21861,7 +21861,7 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21957,7 +21957,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22005,7 +22005,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L386" t="inlineStr"/>
@@ -22053,7 +22053,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L387" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22149,7 +22149,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25613,7 +25613,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25626,12 +25626,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25949,7 +25949,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -25997,7 +25997,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26010,12 +26010,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27293,7 +27293,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27306,12 +27306,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28218,12 +28218,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28301,7 +28301,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28314,12 +28314,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29453,7 +29453,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29501,7 +29501,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30845,7 +30845,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -30858,12 +30858,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -30906,12 +30906,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31277,7 +31277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31290,12 +31290,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31386,12 +31386,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31578,12 +31578,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33245,7 +33245,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33258,12 +33258,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -33978,12 +33978,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34829,7 +34829,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -34842,12 +34842,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35741,7 +35741,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -35754,12 +35754,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -35789,7 +35789,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -35802,12 +35802,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -35837,7 +35837,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -35850,12 +35850,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -35981,7 +35981,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -35994,12 +35994,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36077,7 +36077,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36269,7 +36269,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36282,12 +36282,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36557,7 +36557,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36570,12 +36570,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36701,7 +36701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -36714,12 +36714,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -36749,7 +36749,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -36762,12 +36762,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -36810,12 +36810,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36941,7 +36941,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37085,7 +37085,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37098,12 +37098,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37181,7 +37181,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37194,12 +37194,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38093,7 +38093,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38106,12 +38106,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38141,7 +38141,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38154,12 +38154,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38237,7 +38237,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38250,12 +38250,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38298,12 +38298,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38333,7 +38333,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38346,12 +38346,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39149,7 +39149,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39162,12 +39162,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39197,7 +39197,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39210,12 +39210,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39245,7 +39245,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39258,12 +39258,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39293,7 +39293,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39306,12 +39306,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39389,7 +39389,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39402,12 +39402,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22733,7 +22733,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22746,12 +22746,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -22781,7 +22781,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25613,7 +25613,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25626,12 +25626,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -25914,12 +25914,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -25949,7 +25949,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -25997,7 +25997,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26010,12 +26010,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27293,7 +27293,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27306,12 +27306,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28781,7 +28781,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -28794,12 +28794,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30845,7 +30845,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -30858,12 +30858,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -30906,12 +30906,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31277,7 +31277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31290,12 +31290,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31386,12 +31386,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -32778,12 +32778,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -32826,12 +32826,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33245,7 +33245,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33258,12 +33258,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33293,7 +33293,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33306,12 +33306,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33437,7 +33437,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33450,12 +33450,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -33978,12 +33978,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34829,7 +34829,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -34842,12 +34842,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35226,12 +35226,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35261,7 +35261,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35274,12 +35274,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35549,7 +35549,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35562,12 +35562,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35789,7 +35789,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -35802,12 +35802,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -35981,7 +35981,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -35994,12 +35994,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36269,7 +36269,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36282,12 +36282,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36557,7 +36557,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36570,12 +36570,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36701,7 +36701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -36714,12 +36714,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -36749,7 +36749,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -36762,12 +36762,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -36810,12 +36810,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36941,7 +36941,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37325,7 +37325,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37338,12 +37338,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38189,7 +38189,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38202,12 +38202,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38237,7 +38237,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38250,12 +38250,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38381,7 +38381,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38394,12 +38394,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38429,7 +38429,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38442,12 +38442,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39197,7 +39197,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39210,12 +39210,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39245,7 +39245,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39258,12 +39258,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39293,7 +39293,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39306,12 +39306,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22733,7 +22733,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22746,12 +22746,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -22781,7 +22781,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25613,7 +25613,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25626,12 +25626,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -25914,12 +25914,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -25949,7 +25949,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -25997,7 +25997,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26010,12 +26010,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27293,7 +27293,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27306,12 +27306,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28218,12 +28218,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28301,7 +28301,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28314,12 +28314,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28781,7 +28781,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -28794,12 +28794,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31277,7 +31277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31290,12 +31290,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31386,12 +31386,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31578,12 +31578,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -32778,12 +32778,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -32826,12 +32826,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33245,7 +33245,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33258,12 +33258,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33293,7 +33293,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33306,12 +33306,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33437,7 +33437,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33450,12 +33450,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33917,7 +33917,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -33930,12 +33930,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -33978,12 +33978,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34829,7 +34829,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -34842,12 +34842,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35226,12 +35226,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35261,7 +35261,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35274,12 +35274,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35309,7 +35309,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35405,7 +35405,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35418,12 +35418,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35549,7 +35549,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35562,12 +35562,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35741,7 +35741,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -35754,12 +35754,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -35789,7 +35789,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -35802,12 +35802,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -35837,7 +35837,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -35850,12 +35850,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -35981,7 +35981,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -35994,12 +35994,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36077,7 +36077,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36701,7 +36701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -36714,12 +36714,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -36749,7 +36749,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -36762,12 +36762,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -36810,12 +36810,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36941,7 +36941,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37181,7 +37181,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37194,12 +37194,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37325,7 +37325,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37338,12 +37338,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39149,7 +39149,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39162,12 +39162,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39197,7 +39197,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39210,12 +39210,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39245,7 +39245,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39258,12 +39258,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39293,7 +39293,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39306,12 +39306,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39389,7 +39389,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39402,12 +39402,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22733,7 +22733,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22746,12 +22746,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -25914,12 +25914,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28218,12 +28218,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28301,7 +28301,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28314,12 +28314,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29453,7 +29453,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29501,7 +29501,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30845,7 +30845,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -30858,12 +30858,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31386,12 +31386,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33293,7 +33293,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33306,12 +33306,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33917,7 +33917,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -33930,12 +33930,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34157,7 +34157,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34170,12 +34170,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35226,12 +35226,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35261,7 +35261,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35274,12 +35274,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35309,7 +35309,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35405,7 +35405,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35418,12 +35418,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35549,7 +35549,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35562,12 +35562,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35741,7 +35741,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -35754,12 +35754,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -35789,7 +35789,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -35802,12 +35802,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -35837,7 +35837,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -35850,12 +35850,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -35981,7 +35981,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -35994,12 +35994,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36077,7 +36077,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36557,7 +36557,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36570,12 +36570,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -36810,12 +36810,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36941,7 +36941,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37181,7 +37181,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37194,12 +37194,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38093,7 +38093,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38106,12 +38106,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38141,7 +38141,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38154,12 +38154,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38189,7 +38189,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38202,12 +38202,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38237,7 +38237,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38250,12 +38250,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38298,12 +38298,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38333,7 +38333,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38346,12 +38346,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38381,7 +38381,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38394,12 +38394,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38429,7 +38429,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38442,12 +38442,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39389,7 +39389,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39402,12 +39402,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22733,7 +22733,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22746,12 +22746,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -22781,7 +22781,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25613,7 +25613,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25626,12 +25626,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -25914,12 +25914,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -25997,7 +25997,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26010,12 +26010,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28301,7 +28301,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28314,12 +28314,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28781,7 +28781,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -28794,12 +28794,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29453,7 +29453,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29501,7 +29501,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30845,7 +30845,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -30858,12 +30858,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31386,12 +31386,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31578,12 +31578,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -32826,12 +32826,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33245,7 +33245,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33258,12 +33258,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33437,7 +33437,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33450,12 +33450,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33917,7 +33917,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -33930,12 +33930,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -33978,12 +33978,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34829,7 +34829,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -34842,12 +34842,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35226,12 +35226,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35261,7 +35261,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35274,12 +35274,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35309,7 +35309,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35405,7 +35405,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35418,12 +35418,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35549,7 +35549,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35562,12 +35562,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36269,7 +36269,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36282,12 +36282,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36557,7 +36557,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36570,12 +36570,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36701,7 +36701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -36714,12 +36714,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -36749,7 +36749,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -36762,12 +36762,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -36810,12 +36810,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36941,7 +36941,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37085,7 +37085,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37098,12 +37098,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37181,7 +37181,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37194,12 +37194,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37325,7 +37325,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37338,12 +37338,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38093,7 +38093,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38106,12 +38106,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38141,7 +38141,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38154,12 +38154,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38189,7 +38189,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38202,12 +38202,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38237,7 +38237,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38250,12 +38250,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38298,12 +38298,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38333,7 +38333,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38346,12 +38346,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38381,7 +38381,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38394,12 +38394,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38429,7 +38429,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38442,12 +38442,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39245,7 +39245,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39258,12 +39258,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39293,7 +39293,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39306,12 +39306,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22733,7 +22733,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22746,12 +22746,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -22781,7 +22781,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23453,7 +23453,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -23501,7 +23501,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23514,12 +23514,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25229,7 +25229,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25613,7 +25613,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25626,12 +25626,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -25914,12 +25914,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -25949,7 +25949,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -25997,7 +25997,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26010,12 +26010,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27293,7 +27293,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27306,12 +27306,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28218,12 +28218,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28301,7 +28301,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28314,12 +28314,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28781,7 +28781,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -28794,12 +28794,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29453,7 +29453,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29501,7 +29501,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -30906,12 +30906,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31277,7 +31277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31290,12 +31290,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31386,12 +31386,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31578,12 +31578,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -32778,12 +32778,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -32826,12 +32826,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33245,7 +33245,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33258,12 +33258,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33293,7 +33293,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33306,12 +33306,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33437,7 +33437,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33450,12 +33450,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33917,7 +33917,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -33930,12 +33930,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -33978,12 +33978,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34157,7 +34157,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34170,12 +34170,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34829,7 +34829,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -34842,12 +34842,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35021,7 +35021,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35034,12 +35034,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35261,7 +35261,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35274,12 +35274,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35309,7 +35309,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35405,7 +35405,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35418,12 +35418,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35549,7 +35549,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35562,12 +35562,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35645,7 +35645,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35741,7 +35741,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -35754,12 +35754,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -35981,7 +35981,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -35994,12 +35994,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36077,7 +36077,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36269,7 +36269,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36282,12 +36282,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36557,7 +36557,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36570,12 +36570,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36701,7 +36701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -36714,12 +36714,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -36749,7 +36749,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -36762,12 +36762,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -36810,12 +36810,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36941,7 +36941,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37085,7 +37085,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37098,12 +37098,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37325,7 +37325,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37338,12 +37338,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38093,7 +38093,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38106,12 +38106,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38141,7 +38141,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38154,12 +38154,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38189,7 +38189,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38202,12 +38202,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38298,12 +38298,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38333,7 +38333,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38346,12 +38346,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38381,7 +38381,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38394,12 +38394,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38429,7 +38429,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38442,12 +38442,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38573,7 +38573,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38586,12 +38586,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39149,7 +39149,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39162,12 +39162,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39197,7 +39197,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39210,12 +39210,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39245,7 +39245,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39258,12 +39258,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39293,7 +39293,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39306,12 +39306,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39389,7 +39389,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39402,12 +39402,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22781,7 +22781,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23213,7 +23213,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -23309,7 +23309,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -23549,7 +23549,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -23597,7 +23597,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23610,12 +23610,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23885,7 +23885,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F426" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24138,12 +24138,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25037,7 +25037,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25133,7 +25133,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25194,12 +25194,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25517,7 +25517,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25565,7 +25565,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25613,7 +25613,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25626,12 +25626,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27149,7 +27149,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27162,12 +27162,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27245,7 +27245,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27258,12 +27258,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27293,7 +27293,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27306,12 +27306,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28218,12 +28218,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29693,7 +29693,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29706,12 +29706,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30077,7 +30077,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30090,12 +30090,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -30906,12 +30906,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31277,7 +31277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31290,12 +31290,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31578,12 +31578,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -31866,12 +31866,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -31901,7 +31901,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -31914,12 +31914,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31949,7 +31949,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -31962,12 +31962,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -31997,7 +31997,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32010,12 +32010,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32045,7 +32045,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32058,12 +32058,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32141,7 +32141,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32189,7 +32189,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32202,12 +32202,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32237,7 +32237,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32250,12 +32250,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32285,7 +32285,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32298,12 +32298,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32490,12 +32490,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -32778,12 +32778,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -32826,12 +32826,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33245,7 +33245,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33258,12 +33258,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33498,12 +33498,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34157,7 +34157,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34170,12 +34170,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -34829,7 +34829,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -34842,12 +34842,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -34877,7 +34877,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -34890,12 +34890,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -34938,12 +34938,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -34986,12 +34986,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35069,7 +35069,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35082,12 +35082,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35117,7 +35117,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35130,12 +35130,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35165,7 +35165,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35178,12 +35178,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35226,12 +35226,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35357,7 +35357,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35370,12 +35370,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35453,7 +35453,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35501,7 +35501,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35514,12 +35514,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35597,7 +35597,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35610,12 +35610,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35706,12 +35706,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -35741,7 +35741,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -35754,12 +35754,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -35789,7 +35789,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -35802,12 +35802,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -35837,7 +35837,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -35850,12 +35850,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -35885,7 +35885,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -35933,7 +35933,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -35946,12 +35946,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -36029,7 +36029,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36077,7 +36077,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36090,12 +36090,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36138,12 +36138,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36173,7 +36173,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36186,12 +36186,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36221,7 +36221,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36234,12 +36234,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36317,7 +36317,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36330,12 +36330,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36365,7 +36365,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36378,12 +36378,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36413,7 +36413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36426,12 +36426,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36461,7 +36461,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36474,12 +36474,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36509,7 +36509,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36522,12 +36522,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36653,7 +36653,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -36701,7 +36701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -36714,12 +36714,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -36797,7 +36797,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -36810,12 +36810,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -36845,7 +36845,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -36858,12 +36858,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -36989,7 +36989,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37002,12 +37002,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37085,7 +37085,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37098,12 +37098,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37133,7 +37133,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37146,12 +37146,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37181,7 +37181,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37194,12 +37194,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37229,7 +37229,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37277,7 +37277,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37290,12 +37290,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37325,7 +37325,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37338,12 +37338,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37373,7 +37373,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37421,7 +37421,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37434,12 +37434,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37469,7 +37469,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37517,7 +37517,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37530,12 +37530,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37565,7 +37565,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37578,12 +37578,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37613,7 +37613,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37626,12 +37626,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37661,7 +37661,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -37709,7 +37709,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -37722,12 +37722,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -37757,7 +37757,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -37770,12 +37770,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -37805,7 +37805,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -37818,12 +37818,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -37853,7 +37853,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -37866,12 +37866,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -37962,12 +37962,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -37997,7 +37997,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38010,12 +38010,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38045,7 +38045,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38058,12 +38058,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38093,7 +38093,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38106,12 +38106,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38141,7 +38141,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38154,12 +38154,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38189,7 +38189,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38202,12 +38202,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38237,7 +38237,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38250,12 +38250,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38285,7 +38285,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38298,12 +38298,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38381,7 +38381,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38394,12 +38394,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38429,7 +38429,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38442,12 +38442,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38477,7 +38477,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38490,12 +38490,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38538,12 +38538,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38621,7 +38621,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38634,12 +38634,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38669,7 +38669,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38717,7 +38717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -38765,7 +38765,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -38778,12 +38778,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -38813,7 +38813,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -38909,7 +38909,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -38922,12 +38922,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -38957,7 +38957,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -38970,12 +38970,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39005,7 +39005,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39018,12 +39018,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39053,7 +39053,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39066,12 +39066,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39101,7 +39101,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39114,12 +39114,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39197,7 +39197,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39210,12 +39210,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39245,7 +39245,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39258,12 +39258,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39293,7 +39293,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39306,12 +39306,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39341,7 +39341,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39389,7 +39389,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39402,12 +39402,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39437,7 +39437,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39450,12 +39450,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39485,7 +39485,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39498,12 +39498,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39581,7 +39581,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39594,12 +39594,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39629,7 +39629,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39642,12 +39642,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39677,7 +39677,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -39725,7 +39725,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -39738,12 +39738,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -39821,7 +39821,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -39834,12 +39834,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -39917,7 +39917,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -39930,12 +39930,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -39965,7 +39965,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -39978,12 +39978,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -22205,7 +22205,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,12 +22218,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22253,7 +22253,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -22301,7 +22301,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -22397,7 +22397,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -22493,7 +22493,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -22589,7 +22589,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -22637,7 +22637,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -22685,7 +22685,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -22877,7 +22877,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -22938,12 +22938,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -22973,7 +22973,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -22986,12 +22986,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -23069,7 +23069,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -23117,7 +23117,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23130,12 +23130,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23178,12 +23178,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23706,12 +23706,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -23754,12 +23754,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -23789,7 +23789,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -23837,7 +23837,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -23850,12 +23850,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -23981,7 +23981,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -24077,7 +24077,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24090,12 +24090,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -24173,7 +24173,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24186,12 +24186,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24234,12 +24234,12 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24330,12 +24330,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24365,7 +24365,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24378,12 +24378,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24413,7 +24413,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24461,7 +24461,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24509,7 +24509,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24557,7 +24557,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24605,7 +24605,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24653,7 +24653,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24666,12 +24666,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24701,7 +24701,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -24749,7 +24749,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -24797,7 +24797,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -24810,12 +24810,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -24845,7 +24845,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -24941,7 +24941,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -24989,7 +24989,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25085,7 +25085,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25098,12 +25098,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -25277,7 +25277,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25290,12 +25290,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25325,7 +25325,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25373,7 +25373,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25421,7 +25421,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25469,7 +25469,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25482,12 +25482,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25661,7 +25661,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25674,12 +25674,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -25709,7 +25709,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -25770,12 +25770,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -25805,7 +25805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -25818,12 +25818,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -25866,12 +25866,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -25914,12 +25914,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -25949,7 +25949,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26045,7 +26045,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26106,12 +26106,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26237,7 +26237,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26285,7 +26285,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26298,12 +26298,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26333,7 +26333,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26346,12 +26346,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26381,7 +26381,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26394,12 +26394,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26429,7 +26429,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26442,12 +26442,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26490,12 +26490,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26525,7 +26525,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26573,7 +26573,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26621,7 +26621,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26634,12 +26634,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26669,7 +26669,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26682,12 +26682,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26717,7 +26717,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -26730,12 +26730,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -26813,7 +26813,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -26826,12 +26826,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -26874,12 +26874,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26909,7 +26909,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -26922,12 +26922,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -26970,12 +26970,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27053,7 +27053,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27066,12 +27066,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27101,7 +27101,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27197,7 +27197,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27293,7 +27293,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27306,12 +27306,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27341,7 +27341,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27354,12 +27354,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27437,7 +27437,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27450,12 +27450,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27485,7 +27485,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27533,7 +27533,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27546,12 +27546,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27629,7 +27629,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27642,12 +27642,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27677,7 +27677,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -27725,7 +27725,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -27738,12 +27738,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -27773,7 +27773,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -27821,7 +27821,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -27834,12 +27834,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -27869,7 +27869,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -27882,12 +27882,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -27930,12 +27930,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27965,7 +27965,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -27978,12 +27978,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28013,7 +28013,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28061,7 +28061,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28109,7 +28109,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28157,7 +28157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28170,12 +28170,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28205,7 +28205,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28218,12 +28218,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28253,7 +28253,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28266,12 +28266,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28301,7 +28301,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28314,12 +28314,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28349,7 +28349,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28362,12 +28362,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28410,12 +28410,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28445,7 +28445,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28493,7 +28493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28541,7 +28541,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28589,7 +28589,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28602,12 +28602,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28685,7 +28685,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28698,12 +28698,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28733,7 +28733,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -28842,12 +28842,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -28890,12 +28890,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28973,7 +28973,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -28986,12 +28986,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29021,7 +29021,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29034,12 +29034,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29069,7 +29069,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29082,12 +29082,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29117,7 +29117,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29165,7 +29165,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29178,12 +29178,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29213,7 +29213,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29226,12 +29226,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29261,7 +29261,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29309,7 +29309,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29357,7 +29357,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29370,12 +29370,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29405,7 +29405,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29418,12 +29418,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29453,7 +29453,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29501,7 +29501,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29514,12 +29514,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29597,7 +29597,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29610,12 +29610,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29645,7 +29645,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29658,12 +29658,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29789,7 +29789,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -29837,7 +29837,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -29885,7 +29885,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29981,7 +29981,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -29994,12 +29994,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30125,7 +30125,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30173,7 +30173,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30186,12 +30186,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30221,7 +30221,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30234,12 +30234,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30269,7 +30269,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30282,12 +30282,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30317,7 +30317,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30365,7 +30365,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30378,12 +30378,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30461,7 +30461,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30474,12 +30474,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30509,7 +30509,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30605,7 +30605,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30618,12 +30618,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30666,12 +30666,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30701,7 +30701,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30714,12 +30714,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -30762,12 +30762,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -30797,7 +30797,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -30845,7 +30845,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -30858,12 +30858,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -30906,12 +30906,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -30941,7 +30941,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -30954,12 +30954,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30989,7 +30989,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31002,12 +31002,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31037,7 +31037,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31050,12 +31050,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31098,12 +31098,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31133,7 +31133,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31181,7 +31181,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31229,7 +31229,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31242,12 +31242,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31277,7 +31277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31290,12 +31290,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31325,7 +31325,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31338,12 +31338,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31434,12 +31434,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31469,7 +31469,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31517,7 +31517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31578,12 +31578,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31613,7 +31613,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31661,7 +31661,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31674,12 +31674,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31709,7 +31709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -31722,12 +31722,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31757,7 +31757,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -31805,7 +31805,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32333,7 +32333,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32346,12 +32346,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32381,7 +32381,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32394,12 +32394,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32429,7 +32429,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32442,12 +32442,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32525,7 +32525,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32573,7 +32573,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32586,12 +32586,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32621,7 +32621,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32669,7 +32669,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32682,12 +32682,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32717,7 +32717,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -32730,12 +32730,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32765,7 +32765,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -32778,12 +32778,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -32826,12 +32826,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32861,7 +32861,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -32909,7 +32909,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -32957,7 +32957,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33005,7 +33005,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33066,12 +33066,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33101,7 +33101,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33114,12 +33114,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33162,12 +33162,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33197,7 +33197,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33210,12 +33210,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33245,7 +33245,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33258,12 +33258,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33293,7 +33293,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33306,12 +33306,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33341,7 +33341,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33354,12 +33354,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33402,12 +33402,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33437,7 +33437,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33450,12 +33450,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33581,7 +33581,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33594,12 +33594,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33629,7 +33629,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33677,7 +33677,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33690,12 +33690,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -33738,12 +33738,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -33773,7 +33773,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -33821,7 +33821,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -33869,7 +33869,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -33882,12 +33882,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -33917,7 +33917,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -33930,12 +33930,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -33978,12 +33978,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34013,7 +34013,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34074,12 +34074,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34109,7 +34109,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34122,12 +34122,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34157,7 +34157,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34170,12 +34170,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34205,7 +34205,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34218,12 +34218,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34266,12 +34266,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34349,7 +34349,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34397,7 +34397,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34410,12 +34410,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34445,7 +34445,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34458,12 +34458,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34493,7 +34493,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34541,7 +34541,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34589,7 +34589,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34602,12 +34602,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34637,7 +34637,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34685,7 +34685,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34698,12 +34698,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -34733,7 +34733,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -34746,12 +34746,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -34781,7 +34781,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -34794,12 +34794,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>